--- a/OV-Maintenance/check_reconstructed.xlsx
+++ b/OV-Maintenance/check_reconstructed.xlsx
@@ -2261,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2538,9 +2538,65 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>5-10</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>전체 VM(virt-launcher) Pod의 memory request 확인</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>oc get pods -A -l kubevirt.io=virt-launcher -o custom-columns=NS:.metadata.namespace,NAME:.metadata.name,NODE:.spec.nodeName,REQ:.spec.containers[*].resources.requests.memory</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>각 VM(virt-launcher Pod)의 memory request가 설계값과 일치하고 특정 노드에 편중되지 않음</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>[신규] 2026-09-14 추가</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>5-11</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>VM 스케줄링 실패(FailedScheduling) 이벤트 확인</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>oc get events -A --field-selector reason=FailedScheduling --sort-by=.lastTimestamp</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>FailedScheduling 이벤트 없음(있으면 사유를 확인해 request 소진/오버커밋 여부 판단)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>[신규] 2026-09-14 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>※ 본 시트는 OCP 공통 점검 항목에 포함되지 않은 CNV(Virtualization) 고유 점검 제안 항목입니다.</t>
         </is>
@@ -2548,7 +2604,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OV-Maintenance/check_reconstructed.xlsx
+++ b/OV-Maintenance/check_reconstructed.xlsx
@@ -875,32 +875,28 @@
       <c r="F4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>VM 스케줄링 가능 Node의 kubevirt.io/schedulable 라벨을 확인한다.</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>oc get nodes -l kubevirt.io/schedulable=true</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>CNV 설치 대상 Worker/Infra 노드에 라벨이 정상 부여되어 있고 설계 노드 수와 일치</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>[신규] 2026-09-11 추가</t>
-        </is>
-      </c>
+      <c r="F5" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2222,33 +2218,29 @@
       <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>4-5</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Multus/OVN-Kubernetes 네트워크 플러그인 Pod 상태 확인</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>oc get pods -n openshift-multus
 oc get pods -n openshift-ovn-kubernetes</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>모든 Pod의 STATUS가 Running이고 RESTARTS가 비정상적으로 높지 않음</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>[신규] 2026-09-11 추가</t>
-        </is>
-      </c>
+      <c r="F6" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2453,148 +2445,127 @@
       <c r="F7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>5-7</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>KubeVirt/CDI 플랫폼 컴포넌트 상태 확인 (HyperConverged CR, virt-*, cdi-* Pod)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>oc get hco -n openshift-cnv
 oc get pods -n openshift-cnv -l kubevirt.io</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>HyperConverged AVAILABLE=True·DEGRADED=False, virt-operator/virt-controller/virt-handler/virt-api 및 cdi-* Pod 모두 Running</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>[신규] 2026-09-11 추가</t>
-        </is>
-      </c>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>5-8</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>노드별 메모리 Capacity/Allocatable/Allocated(Request 소진율) 확인</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>oc describe node &lt;각 노드&gt;
 oc describe node &lt;각 노드&gt; | grep -A10 'Allocated resources'</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Allocatable 대비 Allocated(Requests) 소진율이 과도하게 높지 않음 (오버커밋으로 인한 VM 스케줄링 실패 여지 확인)</t>
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>[신규] 2026-09-14 추가</t>
-        </is>
-      </c>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>OpenShift Virtualization 메모리 Overcommit(higherWorkloadDensity) 설정 확인</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>oc get hyperconverged kubevirt-hyperconverged -n openshift-cnv -o jsonpath={.spec.higherWorkloadDensity}</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>조직 정책과 일치하는 Overcommit 설정 값인지 확인 (미설정 시 기본 비활성)</t>
         </is>
       </c>
       <c r="E10" s="8" t="n"/>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>[신규] 2026-09-14 추가</t>
-        </is>
-      </c>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>5-10</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>전체 VM(virt-launcher) Pod의 memory request 확인</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>oc get pods -A -l kubevirt.io=virt-launcher -o custom-columns=NS:.metadata.namespace,NAME:.metadata.name,NODE:.spec.nodeName,REQ:.spec.containers[*].resources.requests.memory</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>각 VM(virt-launcher Pod)의 memory request가 설계값과 일치하고 특정 노드에 편중되지 않음</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>[신규] 2026-09-14 추가</t>
-        </is>
-      </c>
+      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>VM 스케줄링 실패(FailedScheduling) 이벤트 확인</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>oc get events -A --field-selector reason=FailedScheduling --sort-by=.lastTimestamp</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>FailedScheduling 이벤트 없음(있으면 사유를 확인해 request 소진/오버커밋 여부 판단)</t>
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>[신규] 2026-09-14 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>

--- a/OV-Maintenance/check_reconstructed.xlsx
+++ b/OV-Maintenance/check_reconstructed.xlsx
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1719,6 +1719,54 @@
       </c>
       <c r="E33" s="8" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2-33</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>control-plane-machine-set</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>oc get co control-plane-machine-set</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>AVAILABLE=True, PROGRESSING=False, DEGRADED=False</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>2-34</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>olm</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>oc get co olm</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>AVAILABLE=True, PROGRESSING=False, DEGRADED=False</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1789,7 +1837,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>3-1-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -1814,7 +1862,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>3-1-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1839,7 +1887,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>3-1-3</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1864,7 +1912,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>3-1-4</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1889,7 +1937,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>3-1-5</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1914,7 +1962,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>3-1-6</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1939,7 +1987,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>3-1-7</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1975,7 +2023,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>3-2-1</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1999,7 +2047,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>3-2-2</t>
+          <t>3-9</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2035,7 +2083,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>3-3-1</t>
+          <t>3-10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">

--- a/OV-Maintenance/check_reconstructed.xlsx
+++ b/OV-Maintenance/check_reconstructed.xlsx
@@ -1779,7 +1779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2103,6 +2103,30 @@
       </c>
       <c r="E14" s="8" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>3-11</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>정지된(non-Running) Pod 리스트 조회, Job/DaemonSet 정상 종료와 비정상 종료 구분</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>oc get pods -A --field-selector=status.phase!=Running</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>정상 종료(Job/DaemonSet 소유 Succeeded)와 비정상 종료(Failed/Pending/Unknown 등)가 구분되어 출력, 비정상 종료 항목 없음 또는 사유 확인됨</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2301,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2614,8 +2638,33 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="7" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>5-12</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>VM 실행 정책(spec.running/runStrategy) 설정 확인</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>oc get vm -A -o custom-columns=NAME:.metadata.name,RUNNING:.spec.running,RUNSTRATEGY:.spec.runStrategy</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>spec.running(deprecated) 필드가 남아있지 않고, runStrategy가 RerunOnFailure로 설정됨 — 아니면 확인 필요</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>※ 본 시트는 OCP 공통 점검 항목에 포함되지 않은 CNV(Virtualization) 고유 점검 제안 항목입니다.</t>
         </is>
@@ -2623,7 +2672,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OV-Maintenance/check_reconstructed.xlsx
+++ b/OV-Maintenance/check_reconstructed.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -897,6 +897,31 @@
       </c>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>노드별 스펙(CPU/Memory Capacity) 및 현재 리소스 사용량 확인</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>oc describe node | grep -A2 Capacity
+oc adm top node</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>에러 없이 노드별 CPU/Memory Capacity와 현재 사용량(top) 출력</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1779,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2088,17 +2113,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>특정 Pod에서 출력한 로깅 메시지를 조회한다.</t>
+          <t>정지된(non-Running) Pod 리스트 조회, Job/DaemonSet 정상 종료와 비정상 종료 구분</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>oc logs &lt;pod-name&gt; -n &lt;ns-name&gt;</t>
+          <t>oc get pods -A --field-selector=status.phase!=Running</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>에러 없이 로그 스트림 정상 출력</t>
+          <t>정상 종료(Job/DaemonSet 소유 Succeeded)와 비정상 종료(Failed/Pending/Unknown 등)가 구분되어 출력, 비정상 종료 항목 없음 또는 사유 확인됨</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr"/>
@@ -2112,21 +2137,46 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>정지된(non-Running) Pod 리스트 조회, Job/DaemonSet 정상 종료와 비정상 종료 구분</t>
+          <t>특정 Pod에서 출력한 로깅 메시지를 조회한다.</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>oc get pods -A --field-selector=status.phase!=Running</t>
+          <t>oc logs &lt;pod-name&gt; -n &lt;ns-name&gt;</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>정상 종료(Job/DaemonSet 소유 Succeeded)와 비정상 종료(Failed/Pending/Unknown 등)가 구분되어 출력, 비정상 종료 항목 없음 또는 사유 확인됨</t>
+          <t>에러 없이 로그 스트림 정상 출력</t>
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>3-12</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>kube-apiserver Health / kubelet 상태 확인</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>oc get --raw /healthz
+oc get nodes (kubelet Ready 조건)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>healthz가 'ok' 반환, 모든 노드 kubelet Ready=True</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2662,7 +2712,6 @@
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="7" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>

--- a/OV-Maintenance/check_reconstructed.xlsx
+++ b/OV-Maintenance/check_reconstructed.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -922,6 +922,31 @@
       </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Machine Config(MCP) 현황 확인</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>oc get mcp
+oc get nodes (currentConfig vs desiredConfig)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>MCP가 UPDATED=True/UPDATING=False/DEGRADED=False/READY=TOTAL, 전 노드 current==desired MachineConfig</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
